--- a/APS-Modules/aps-cd90/src/main/resources/excelModel/cd90ScheduleResult.xlsx
+++ b/APS-Modules/aps-cd90/src/main/resources/excelModel/cd90ScheduleResult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-cd90\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F38FF71-06CF-40B1-9F73-5498B0D669D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160C6BA5-9276-44D6-9E7B-FB94DBD72413}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="23265" windowHeight="12465" tabRatio="596" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,48 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
-  <si>
-    <t>2026年06月06日全钢裁断工程生产计划单</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>成型余量</t>
   </si>
   <si>
-    <t>早班06/05</t>
-  </si>
-  <si>
-    <t>中班06/05</t>
-  </si>
-  <si>
-    <t>夜班06/06</t>
-  </si>
-  <si>
-    <t>早班06/06</t>
-  </si>
-  <si>
     <t>计划</t>
   </si>
   <si>
     <t>实际</t>
-  </si>
-  <si>
-    <t>G1301</t>
-  </si>
-  <si>
-    <t>DFG81001</t>
-  </si>
-  <si>
-    <t>CSTA6023</t>
-  </si>
-  <si>
-    <t>G31-6,G31-7</t>
-  </si>
-  <si>
-    <t>H1104</t>
-  </si>
-  <si>
-    <t>315/80R22.5 JF518四层</t>
   </si>
   <si>
     <t>库存（米）
@@ -103,6 +70,81 @@
   </si>
   <si>
     <t>结构名称</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>{planDate}全钢裁断工程生产计划单</t>
+  </si>
+  <si>
+    <t>中班{previousDate2}</t>
+  </si>
+  <si>
+    <t>{.machineCode}</t>
+  </si>
+  <si>
+    <t>{.unitConsume}</t>
+  </si>
+  <si>
+    <t>{.planSurplusQty}</t>
+  </si>
+  <si>
+    <t>{.clothCode}</t>
+  </si>
+  <si>
+    <t>{.bigRollCode}</t>
+  </si>
+  <si>
+    <t>{.stockQty}</t>
+  </si>
+  <si>
+    <t>{.storageLaneCode}</t>
+  </si>
+  <si>
+    <t>{.previousClass3PlanQty}</t>
+  </si>
+  <si>
+    <t>{.previousClass3FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class1PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class1FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class2PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class2FinishQty}</t>
+  </si>
+  <si>
+    <t>{.class3PlanQty}</t>
+  </si>
+  <si>
+    <t>{.class3FinishQty}</t>
+  </si>
+  <si>
+    <t>{.formingPlanQty}</t>
+  </si>
+  <si>
+    <t>{.fourShiftPlanQty}</t>
+  </si>
+  <si>
+    <t>{.cxMachineCodes}</t>
+  </si>
+  <si>
+    <t>{.structureName}</t>
+  </si>
+  <si>
+    <t>夜班{scheduleDate1}</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班{scheduleDate2}</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班{previousDate1}</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -113,7 +155,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="[$-409]d/mmm;@"/>
+    <numFmt numFmtId="177" formatCode="[$-409]d/mmm;@"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -463,16 +505,16 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -785,7 +827,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultColWidth="17.75" defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" style="1" customWidth="1"/>
@@ -802,188 +844,199 @@
     <col min="20" max="16384" width="17.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:19" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="13"/>
+    </row>
+    <row r="3" spans="1:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="13"/>
+      <c r="D3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="15"/>
+      <c r="J3" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="17"/>
+      <c r="L3" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="19"/>
+      <c r="N3" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="19"/>
+      <c r="P3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+    </row>
+    <row r="5" spans="1:19" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="D5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="19"/>
-      <c r="N2" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="19"/>
-      <c r="P2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="9" t="s">
+      <c r="I5" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-    </row>
-    <row r="4" spans="1:19" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5">
-        <v>320</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="5">
-        <v>400</v>
-      </c>
-      <c r="I4" s="5">
-        <v>320</v>
-      </c>
-      <c r="J4" s="5">
-        <v>80</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5">
-        <f>100+100+100+100</f>
-        <v>400</v>
-      </c>
-      <c r="Q4" s="5">
-        <f>P4*B4</f>
-        <v>692</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>13</v>
+      <c r="J5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
